--- a/data/dechet.xlsx
+++ b/data/dechet.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="convention" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="71">
   <si>
     <t xml:space="preserve">cle</t>
   </si>
@@ -120,6 +120,9 @@
     <t xml:space="preserve">responsable</t>
   </si>
   <si>
+    <t xml:space="preserve">progression</t>
+  </si>
+  <si>
     <t xml:space="preserve">Candidature ‘100 Territoires d’éléctrification’</t>
   </si>
   <si>
@@ -235,42 +238,6 @@
   </si>
   <si>
     <t xml:space="preserve">taux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fév</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aoû</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Déc</t>
   </si>
 </sst>
 </file>
@@ -374,7 +341,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -404,6 +371,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -837,7 +808,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -859,25 +830,31 @@
       <c r="F1" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="G1" s="8" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>87</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -885,19 +862,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="0" t="n">
         <v>37</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -905,19 +885,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -925,19 +905,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -945,19 +925,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -981,7 +961,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>27</v>
@@ -989,50 +969,50 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1056,22 +1036,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C2" s="1" t="n">
         <f aca="false">SUMIF(A:A,"poste",C:C)</f>
@@ -1084,10 +1064,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>80000</v>
@@ -1099,10 +1079,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>20000</v>
@@ -1114,10 +1094,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>28000</v>
@@ -1129,10 +1109,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>22000</v>
@@ -1163,107 +1143,91 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>70</v>
+      <c r="A2" s="1" t="n">
+        <v>2019</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>71</v>
+      <c r="A3" s="1" t="n">
+        <v>2020</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>72</v>
+      <c r="A4" s="1" t="n">
+        <v>2021</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>73</v>
+      <c r="A5" s="1" t="n">
+        <v>2022</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>74</v>
+      <c r="A6" s="1" t="n">
+        <v>2023</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>75</v>
+      <c r="A7" s="1" t="n">
+        <v>2024</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>76</v>
+      <c r="A8" s="1" t="n">
+        <v>2025</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>68</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>77</v>
+      <c r="A9" s="1" t="n">
+        <v>2026</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>47</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>63</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>53</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>51</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
